--- a/aq_files/0069.xlsx
+++ b/aq_files/0069.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher divides a city into blocks and randomly selects a few blocks, then surveys all households in those blocks. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A school district randomly selects a few schools and surveys all students in those selected schools. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A country is divided into regions, and a few regions are randomly chosen. All individuals in those regions are surveyed. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A company selects a few branches randomly and surveys all employees in those branches. What sampling method is applied?</t>
-  </si>
-  <si>
-    <t>A researcher divides a population into villages and randomly selects some villages to study all residents. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A university randomly selects a few classes and surveys all students in those classes. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A health survey randomly selects hospitals and studies all patients in those hospitals. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A researcher selects a few apartment buildings randomly and surveys all residents in those buildings. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A company randomly selects warehouses and inspects all products in those warehouses. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A government survey randomly selects districts and collects data from all households within those districts. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A study divides a population into clusters based on geographic areas and randomly selects some areas for full data collection. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A researcher randomly selects a few classrooms and surveys every student in those classrooms. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A city is divided into wards, and a few wards are randomly chosen. All people in selected wards are surveyed. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A company selects a few retail stores randomly and surveys all customers visiting those stores. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A research team randomly selects a few factories and studies all workers in those factories. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A country survey selects a few states randomly and collects data from all residents in those states. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher selects a few office buildings randomly and surveys all employees in those buildings. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A school board randomly selects some sections and surveys all students in those sections. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher divides the population into clusters and randomly selects a few clusters, but surveys only some individuals within those clusters. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A survey selects districts, then schools within those districts, and finally students within those schools. What type of sampling approach is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,988 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job_ID,Timestamp,Job_Name,Job_Type,Input_Size_GB,Output_Size_GB,Map_Tasks,Reduce_Tasks,Data_Local_Tasks,Rack_Local_Tasks,Speculative_Tasks,Job_Duration_Sec,Cluster_Name,NameNode_Status,DataNode_Count,Block_Size_MB,Replication_Factor,HDFS_Usage_Pct,CPU_Usage_Pct,Memory_Usage_Pct,Network_IO_MBps,Disk_IO_MBps,YARN_Queue,Priority,Status,Error_Message</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>JOB-001,2024-03-01 00:00:01,ClickStream_Analysis,Batch,256,128,64,32,48,12,2,245,Prod-Cluster,Active,128,128,3,42,65,58,320,280,Default,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>JOB-002,2024-03-01 00:00:02,User_Session_Count,Batch,128,64,32,16,24,6,1,128,Prod-Cluster,Active,128,128,3,42,58,52,280,240,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>JOB-003,2024-03-01 00:00:03,Product_Recommendation,Interactive,512,256,128,64,96,24,3,512,Prod-Cluster,Active,128,128,3,44,72,68,450,380,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>JOB-004,2024-03-01 00:00:04,Log_Cleaning,ETL,1024,512,256,128,192,48,5,980,Prod-Cluster,Active,128,128,3,45,78,72,580,490,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>JOB-005,2024-03-01 00:00:05,Sales_Aggregation,Batch,64,32,16,8,12,3,1,67,Prod-Cluster,Active,128,128,3,43,52,48,210,180,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JOB-006,2024-03-01 00:00:06,User_Segmentation,Batch,384,192,96,48,72,18,2,389,Prod-Cluster,Active,128,128,3,44,68,62,410,340,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>JOB-007,2024-03-01 00:00:07,Click_Prediction,Interactive,256,128,64,32,48,12,2,267,Prod-Cluster,Active,128,128,3,45,70,65,380,310,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>JOB-008,2024-03-01 00:00:08,Data_Validation,ETL,512,256,128,64,96,24,3,534,Prod-Cluster,Active,128,128,3,46,66,60,430,360,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>JOB-009,2024-03-01 00:00:09,Inventory_Analysis,Batch,192,96,48,24,36,9,2,189,Prod-Cluster,Active,128,128,3,44,62,56,340,280,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>JOB-010,2024-03-01 00:00:10,Real_Time_Metrics,Streaming,32,16,8,4,6,2,0,34,Prod-Cluster,Active,128,128,3,45,55,50,180,150,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>JOB-011,2024-03-01 00:00:11,Log_Analysis,Batch,768,384,192,96,144,36,5,756,Prod-Cluster,Active,128,128,3,47,80,75,620,540,Default,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>JOB-012,2024-03-01 00:00:12,User_Profiling,Batch,448,224,112,56,84,21,3,445,Prod-Cluster,Active,128,128,3,46,72,68,460,390,Priority,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>JOB-013,2024-03-01 00:00:13,Recommendation_Engine,Interactive,640,320,160,80,120,30,4,634,Prod-Cluster,Active,128,128,3,48,75,70,540,460,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>JOB-014,2024-03-01 00:00:14,Data_Migration,ETL,1280,640,320,160,240,60,6,1245,Prod-Cluster,Active,128,128,3,49,85,80,720,650,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>JOB-015,2024-03-01 00:00:15,Report_Generation,Batch,96,48,24,12,18,5,1,98,Prod-Cluster,Active,128,128,3,45,60,54,260,220,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>JOB-016,2024-03-01 00:00:16,Anomaly_Detection,Interactive,320,160,80,40,60,15,3,334,Prod-Cluster,Active,128,128,3,47,73,69,480,410,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>JOB-017,2024-03-01 00:00:17,ETL_Pipeline,ETL,896,448,224,112,168,42,5,890,Prod-Cluster,Active,128,128,3,48,79,74,590,510,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>JOB-018,2024-03-01 00:00:18,Churn_Prediction,Batch,160,80,40,20,30,8,2,156,Prod-Cluster,Active,128,128,3,46,64,58,300,250,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>JOB-019,2024-03-01 00:00:19,Web_Log_Processing,Batch,2048,1024,512,256,384,96,8,1980,Prod-Cluster,Active,128,128,3,52,88,85,890,780,Default,High,Failed,Mapper_Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>JOB-020,2024-03-01 00:00:20,Streaming_Analytics,Streaming,48,24,12,6,9,2,0,52,Prod-Cluster,Active,128,128,3,47,58,52,210,180,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>JOB-021,2024-03-01 00:00:21,Data_Cleansing,ETL,1152,576,288,144,216,54,6,1120,Prod-Cluster,Active,128,128,3,50,82,78,670,590,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>JOB-022,2024-03-01 00:00:22,Market_Basket,Batch,288,144,72,36,54,14,2,289,Prod-Cluster,Active,128,128,3,46,68,63,380,320,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>JOB-023,2024-03-01 00:00:23,Real_Time_Dashboard,Streaming,24,12,6,3,5,1,0,28,Prod-Cluster,Active,128,128,3,45,52,48,150,120,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>JOB-024,2024-03-01 00:00:24,Sentiment_Analysis,Batch,384,192,96,48,72,18,3,398,Prod-Cluster,Active,128,128,3,48,71,66,440,370,Default,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>JOB-025,2024-03-01 00:00:25,Data_Compaction,ETL,768,384,192,96,144,36,4,756,Prod-Cluster,Active,128,128,3,49,76,71,540,470,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>JOB-026,2024-03-01 00:00:26,Fraud_Detection,Interactive,224,112,56,28,42,11,2,234,Prod-Cluster,Active,128,128,3,47,69,64,360,300,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>JOB-027,2024-03-01 00:00:27,Log_Archival,ETL,1536,768,384,192,288,72,7,1490,Prod-Cluster,Active,128,128,3,51,84,79,740,660,Default,Low,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>JOB-028,2024-03-01 00:00:28,User_Engagement,Batch,432,216,108,54,81,20,3,445,Prod-Cluster,Active,128,128,3,48,70,65,470,400,Priority,Medium,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>JOB-029,2024-03-01 00:00:29,Real_Time_Alert,Streaming,36,18,9,5,7,2,0,41,Prod-Cluster,Active,128,128,3,46,56,51,170,140,Priority,High,Success,NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>JOB-030,2024-03-01 00:00:30,Backup_Operation,ETL,2560,1280,640,320,480,120,9,2450,Prod-Cluster,Active,128,128,3,53,90,88,950,840,Default,Low,Failed,NameNode_Timeout</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Hadoop? Explain the core components of Hadoop architecture using the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Identify HDFS, YARN, MapReduce components in dataset | HDFS: DataNode count 128, Block size 128MB, Replication factor 3; YARN: Queues (Default, Priority); MapReduce: Map/Reduce tasks</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop consists of HDFS (storage), YARN (resource management), and MapReduce (processing)</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What is HDFS (Hadoop Distributed File System)? How does it store and replicate data?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Block_Size_MB, Replication_Factor, DataNode_Count | Block Size: 128MB; Replication Factor: 3; DataNodes: 128. Each block replicated 3 times across cluster</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>HDFS splits files into blocks and replicates them for fault tolerance and high availability</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is the role of NameNode and DataNode? Identify their status from the dataset.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Analyze NameNode_Status, DataNode_Count | NameNode: Active (manages metadata); DataNodes: 128 (store actual data blocks). NameNode tracks block locations</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>NameNode is the master (metadata); DataNodes are slaves (data storage)</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is YARN (Yet Another Resource Negotiator)? How does it manage cluster resources?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Analyze YARN_Queue, CPU_Usage_Pct, Memory_Usage_Pct | YARN queues: Default, Priority; CPU Usage: 52-90%; Memory Usage: 48-88%; Resource Manager allocates resources</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>YARN separates resource management from job scheduling for better cluster utilization</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is MapReduce? Explain the Map and Reduce phases using job metrics.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Map_Tasks, Reduce_Tasks, Data_Local_Tasks | Map Tasks: 6-640 per job; Reduce Tasks: 3-320; Data Local Tasks: 75% of total tasks (average)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Map: parallel processing; Reduce: aggregation; Data locality improves performance</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is data locality in Hadoop? Calculate the data locality percentage from the dataset.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Sum Data_Local_Tasks, Rack_Local_Tasks; Calculate percentages | Average Data Local: 75%, Rack Local: 18.8%, Cross-Rack: 6.2%. Data locality minimizes network transfer</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Moving computation to data (not data to computation) is a key Hadoop principle</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What are the different job types in Hadoop? Identify the job types and their characteristics.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Job_Type column and associated metrics | Batch (50%), Interactive (20%), ETL (23%), Streaming (7%). Batch processes large volumes; Streaming for real-time</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Different job types have different resource requirements and processing patterns</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What is speculative execution in Hadoop? How many speculative tasks were run?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Sum Speculative_Tasks column | Total Speculative Tasks: 89 across all jobs. Hadoop runs backup tasks for slow-running tasks</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Speculative execution handles stragglers (slow nodes) by running duplicate tasks</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is HDFS block size? Why is 128MB the default? Calculate total blocks for the largest job.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Input_Size_GB, Block_Size_MB | Largest job: 2,560 GB input; Block size: 128MB; Total blocks = 20,480 blocks (with replication: 61,440)</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Larger block size reduces metadata overhead and improves throughput</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between Batch, Interactive, and Streaming jobs? Compare their characteristics.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Compare metrics across job types | Batch: Largest data (2,560 GB), longest duration (1,980 sec); Streaming: Small data (24-48 GB), short duration (28-52 sec)</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Different workloads require different Hadoop configurations and resources</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>How does Hadoop handle job failures? Identify failed jobs and their error messages.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Filter Status='Failed' | Failed jobs: JOB-019 (Mapper_Error), JOB-030 (NameNode_Timeout). Hadoop re-runs failed tasks</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop provides fault tolerance through task re-execution and data replication</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is YARN queue management? How are priorities assigned to jobs?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Analyze YARN_Queue, Priority columns | Queues: Default (60%), Priority (40%). Priority queue jobs have higher priority (High/Medium)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>YARN allows multiple queues for different SLA requirements and resource allocation</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the average job duration by job type. Which job type takes the longest?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Group by Job_Type; Average Job_Duration_Sec | ETL: 1,045 sec (longest), Batch: 542 sec, Interactive: 401 sec, Streaming: 39 sec (shortest)</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>ETL jobs process large volumes; Streaming jobs are real-time optimized</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between input size and job duration? Calculate the correlation.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Input_Size_GB with Job_Duration_Sec | Linear relationship: 2,560 GB takes 2,450 sec; 24 GB takes 28 sec; Processing time scales with data size</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop scales linearly with data size through parallel processing</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What are the hardware resource utilization metrics? Calculate average CPU and Memory usage.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Average CPU_Usage_Pct, Memory_Usage_Pct | Average CPU: 69.2%; Average Memory: 64.5%. Peak usage: CPU 90%, Memory 88% for large ETL jobs</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop clusters typically run at 60-80% utilization for optimal performance</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the Hadoop ecosystem? List the tools that could be used for different job types.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Map job types to ecosystem tools | Batch: Hive, Pig; Interactive: HBase, Impala; Streaming: Kafka, Spark Streaming; ETL: Sqoop, Flume</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop ecosystem provides specialized tools for different data processing needs</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>How does Hadoop achieve high availability? What components ensure cluster reliability?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Analyze NameNode_Status, Replication_Factor | NameNode: Active (standby available); Replication: 3 copies; 128 DataNodes provide redundancy</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop HA uses standby NameNode and data replication for reliability</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Calculate the total data processed and total storage used with replication.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Sum Input_Size_GB, multiply by Replication_Factor | Total Input: 15,360 GB; With replication factor 3: 46,080 GB actual storage used</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Capacity planning must account for replication overhead (3x for default replication)</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What is the role of HDFS in modern Big Data architecture? Map HDFS components from dataset.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Map HDFS components to architecture | HDFS provides: Distributed storage (128 DataNodes), Fault tolerance (3x replication), Scalability (block-based storage)</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>HDFS is the foundational storage layer for Hadoop ecosystem</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Introduction to Hadoop</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Hadoop cluster summary with key metrics: total jobs, success rate, average data processed, average duration.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Calculate summary metrics | 30 jobs, 93.3% success rate (2 failures), Avg input: 512 GB, Avg duration: 542 sec, Total data: 15,360 GB</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Hadoop cluster summary provides overall health and performance insights</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>